--- a/ExportOrderWebServer/Resources/FillBillTemplateSoling.xlsx
+++ b/ExportOrderWebServer/Resources/FillBillTemplateSoling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\source\repos\AxionPlus\ExportOrderWebServer\ExportOrderWebServer\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E0BDB8-F11A-4D51-A74B-B0B7B7060E77}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C13F32-F3BC-413F-8752-F3E490E9AF9A}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="571" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="25580" windowHeight="15260" tabRatio="571" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -177,12 +177,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;&quot;?&quot;&quot;?&quot;_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0\ ;\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="167" formatCode="0.00_)"/>
     <numFmt numFmtId="168" formatCode="0000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -576,7 +578,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -623,8 +625,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -752,8 +755,14 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="41" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="42" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="Comma0" xfId="20" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Currency [0]_   " xfId="21" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Currency_   " xfId="22" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -796,6 +805,7 @@
     <cellStyle name="Обычный 8" xfId="16" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
     <cellStyle name="Обычный 8 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
     <cellStyle name="Обычный 9" xfId="17" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Финансовый" xfId="42" builtinId="3"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1408,8 +1418,8 @@
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="35"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="46"/>
       <c r="G5" s="35"/>
       <c r="H5" s="37"/>
       <c r="I5" s="40"/>
